--- a/导入资料/环境γ辐射剂量率测量记录表.xlsx
+++ b/导入资料/环境γ辐射剂量率测量记录表.xlsx
@@ -1827,7 +1827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1840,11 +1840,16 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1907,25 +1912,50 @@
       </c>
       <c r="K2" s="11" t="inlineStr">
         <is>
+          <t>仪器示值Rγ(6)</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>仪器示值Rγ(7)</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>仪器示值Rγ(8)</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>仪器示值Rγ(9)</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
+          <t>仪器示值Rγ(10)</t>
+        </is>
+      </c>
+      <c r="P2" s="11" t="inlineStr">
+        <is>
           <t>宇宙射线</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="Q2" s="11" t="inlineStr">
         <is>
           <t>k3</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="R2" s="11" t="inlineStr">
         <is>
           <t>平均值</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="S2" s="11" t="inlineStr">
         <is>
           <t>标准差</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="T2" s="11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1949,6 +1979,11 @@
       <c r="M3" s="12" t="inlineStr"/>
       <c r="N3" s="12" t="inlineStr"/>
       <c r="O3" s="12" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="12" t="inlineStr"/>
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr"/>
+      <c r="T3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="14" t="n">
@@ -1968,6 +2003,11 @@
       <c r="M4" s="14" t="inlineStr"/>
       <c r="N4" s="14" t="inlineStr"/>
       <c r="O4" s="14" t="inlineStr"/>
+      <c r="P4" s="14" t="inlineStr"/>
+      <c r="Q4" s="14" t="inlineStr"/>
+      <c r="R4" s="14" t="inlineStr"/>
+      <c r="S4" s="14" t="inlineStr"/>
+      <c r="T4" s="14" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="12" t="n">
@@ -1987,6 +2027,11 @@
       <c r="M5" s="12" t="inlineStr"/>
       <c r="N5" s="12" t="inlineStr"/>
       <c r="O5" s="12" t="inlineStr"/>
+      <c r="P5" s="12" t="inlineStr"/>
+      <c r="Q5" s="12" t="inlineStr"/>
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr"/>
+      <c r="T5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="14" t="n">
@@ -2006,6 +2051,11 @@
       <c r="M6" s="14" t="inlineStr"/>
       <c r="N6" s="14" t="inlineStr"/>
       <c r="O6" s="14" t="inlineStr"/>
+      <c r="P6" s="14" t="inlineStr"/>
+      <c r="Q6" s="14" t="inlineStr"/>
+      <c r="R6" s="14" t="inlineStr"/>
+      <c r="S6" s="14" t="inlineStr"/>
+      <c r="T6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="12" t="n">
@@ -2025,6 +2075,11 @@
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr"/>
+      <c r="P7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="R7" s="12" t="inlineStr"/>
+      <c r="S7" s="12" t="inlineStr"/>
+      <c r="T7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="14" t="n">
@@ -2044,6 +2099,11 @@
       <c r="M8" s="14" t="inlineStr"/>
       <c r="N8" s="14" t="inlineStr"/>
       <c r="O8" s="14" t="inlineStr"/>
+      <c r="P8" s="14" t="inlineStr"/>
+      <c r="Q8" s="14" t="inlineStr"/>
+      <c r="R8" s="14" t="inlineStr"/>
+      <c r="S8" s="14" t="inlineStr"/>
+      <c r="T8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="12" t="n">
@@ -2063,6 +2123,11 @@
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="12" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
+      <c r="P9" s="12" t="inlineStr"/>
+      <c r="Q9" s="12" t="inlineStr"/>
+      <c r="R9" s="12" t="inlineStr"/>
+      <c r="S9" s="12" t="inlineStr"/>
+      <c r="T9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="n">
@@ -2082,6 +2147,11 @@
       <c r="M10" s="14" t="inlineStr"/>
       <c r="N10" s="14" t="inlineStr"/>
       <c r="O10" s="14" t="inlineStr"/>
+      <c r="P10" s="14" t="inlineStr"/>
+      <c r="Q10" s="14" t="inlineStr"/>
+      <c r="R10" s="14" t="inlineStr"/>
+      <c r="S10" s="14" t="inlineStr"/>
+      <c r="T10" s="14" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="12" t="n">
@@ -2101,6 +2171,11 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="12" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
+      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr"/>
+      <c r="R11" s="12" t="inlineStr"/>
+      <c r="S11" s="12" t="inlineStr"/>
+      <c r="T11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="n">
@@ -2120,6 +2195,11 @@
       <c r="M12" s="14" t="inlineStr"/>
       <c r="N12" s="14" t="inlineStr"/>
       <c r="O12" s="14" t="inlineStr"/>
+      <c r="P12" s="14" t="inlineStr"/>
+      <c r="Q12" s="14" t="inlineStr"/>
+      <c r="R12" s="14" t="inlineStr"/>
+      <c r="S12" s="14" t="inlineStr"/>
+      <c r="T12" s="14" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="12" t="n">
@@ -2139,6 +2219,11 @@
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="12" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
+      <c r="P13" s="12" t="inlineStr"/>
+      <c r="Q13" s="12" t="inlineStr"/>
+      <c r="R13" s="12" t="inlineStr"/>
+      <c r="S13" s="12" t="inlineStr"/>
+      <c r="T13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="14" t="n">
@@ -2158,6 +2243,11 @@
       <c r="M14" s="14" t="inlineStr"/>
       <c r="N14" s="14" t="inlineStr"/>
       <c r="O14" s="14" t="inlineStr"/>
+      <c r="P14" s="14" t="inlineStr"/>
+      <c r="Q14" s="14" t="inlineStr"/>
+      <c r="R14" s="14" t="inlineStr"/>
+      <c r="S14" s="14" t="inlineStr"/>
+      <c r="T14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="12" t="n">
@@ -2177,6 +2267,11 @@
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="12" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
+      <c r="P15" s="12" t="inlineStr"/>
+      <c r="Q15" s="12" t="inlineStr"/>
+      <c r="R15" s="12" t="inlineStr"/>
+      <c r="S15" s="12" t="inlineStr"/>
+      <c r="T15" s="12" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="14" t="n">
@@ -2196,6 +2291,11 @@
       <c r="M16" s="14" t="inlineStr"/>
       <c r="N16" s="14" t="inlineStr"/>
       <c r="O16" s="14" t="inlineStr"/>
+      <c r="P16" s="14" t="inlineStr"/>
+      <c r="Q16" s="14" t="inlineStr"/>
+      <c r="R16" s="14" t="inlineStr"/>
+      <c r="S16" s="14" t="inlineStr"/>
+      <c r="T16" s="14" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="12" t="n">
@@ -2215,6 +2315,11 @@
       <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="12" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr"/>
+      <c r="P17" s="12" t="inlineStr"/>
+      <c r="Q17" s="12" t="inlineStr"/>
+      <c r="R17" s="12" t="inlineStr"/>
+      <c r="S17" s="12" t="inlineStr"/>
+      <c r="T17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="14" t="n">
@@ -2234,6 +2339,11 @@
       <c r="M18" s="14" t="inlineStr"/>
       <c r="N18" s="14" t="inlineStr"/>
       <c r="O18" s="14" t="inlineStr"/>
+      <c r="P18" s="14" t="inlineStr"/>
+      <c r="Q18" s="14" t="inlineStr"/>
+      <c r="R18" s="14" t="inlineStr"/>
+      <c r="S18" s="14" t="inlineStr"/>
+      <c r="T18" s="14" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="12" t="n">
@@ -2253,6 +2363,11 @@
       <c r="M19" s="12" t="inlineStr"/>
       <c r="N19" s="12" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr"/>
+      <c r="P19" s="12" t="inlineStr"/>
+      <c r="Q19" s="12" t="inlineStr"/>
+      <c r="R19" s="12" t="inlineStr"/>
+      <c r="S19" s="12" t="inlineStr"/>
+      <c r="T19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="14" t="n">
@@ -2272,6 +2387,11 @@
       <c r="M20" s="14" t="inlineStr"/>
       <c r="N20" s="14" t="inlineStr"/>
       <c r="O20" s="14" t="inlineStr"/>
+      <c r="P20" s="14" t="inlineStr"/>
+      <c r="Q20" s="14" t="inlineStr"/>
+      <c r="R20" s="14" t="inlineStr"/>
+      <c r="S20" s="14" t="inlineStr"/>
+      <c r="T20" s="14" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="12" t="n">
@@ -2291,6 +2411,11 @@
       <c r="M21" s="12" t="inlineStr"/>
       <c r="N21" s="12" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr"/>
+      <c r="P21" s="12" t="inlineStr"/>
+      <c r="Q21" s="12" t="inlineStr"/>
+      <c r="R21" s="12" t="inlineStr"/>
+      <c r="S21" s="12" t="inlineStr"/>
+      <c r="T21" s="12" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="14" t="n">
@@ -2310,6 +2435,11 @@
       <c r="M22" s="14" t="inlineStr"/>
       <c r="N22" s="14" t="inlineStr"/>
       <c r="O22" s="14" t="inlineStr"/>
+      <c r="P22" s="14" t="inlineStr"/>
+      <c r="Q22" s="14" t="inlineStr"/>
+      <c r="R22" s="14" t="inlineStr"/>
+      <c r="S22" s="14" t="inlineStr"/>
+      <c r="T22" s="14" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="12" t="n">
@@ -2329,6 +2459,11 @@
       <c r="M23" s="12" t="inlineStr"/>
       <c r="N23" s="12" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr"/>
+      <c r="P23" s="12" t="inlineStr"/>
+      <c r="Q23" s="12" t="inlineStr"/>
+      <c r="R23" s="12" t="inlineStr"/>
+      <c r="S23" s="12" t="inlineStr"/>
+      <c r="T23" s="12" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="14" t="n">
@@ -2348,6 +2483,11 @@
       <c r="M24" s="14" t="inlineStr"/>
       <c r="N24" s="14" t="inlineStr"/>
       <c r="O24" s="14" t="inlineStr"/>
+      <c r="P24" s="14" t="inlineStr"/>
+      <c r="Q24" s="14" t="inlineStr"/>
+      <c r="R24" s="14" t="inlineStr"/>
+      <c r="S24" s="14" t="inlineStr"/>
+      <c r="T24" s="14" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="12" t="n">
@@ -2367,6 +2507,11 @@
       <c r="M25" s="12" t="inlineStr"/>
       <c r="N25" s="12" t="inlineStr"/>
       <c r="O25" s="12" t="inlineStr"/>
+      <c r="P25" s="12" t="inlineStr"/>
+      <c r="Q25" s="12" t="inlineStr"/>
+      <c r="R25" s="12" t="inlineStr"/>
+      <c r="S25" s="12" t="inlineStr"/>
+      <c r="T25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="14" t="n">
@@ -2386,10 +2531,15 @@
       <c r="M26" s="14" t="inlineStr"/>
       <c r="N26" s="14" t="inlineStr"/>
       <c r="O26" s="14" t="inlineStr"/>
+      <c r="P26" s="14" t="inlineStr"/>
+      <c r="Q26" s="14" t="inlineStr"/>
+      <c r="R26" s="14" t="inlineStr"/>
+      <c r="S26" s="14" t="inlineStr"/>
+      <c r="T26" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:T1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
